--- a/docs/eu/StructureDefinition-ImDiagnosticReport.xlsx
+++ b/docs/eu/StructureDefinition-ImDiagnosticReport.xlsx
@@ -1347,7 +1347,7 @@
     <t>DiagnosticReport.supportingInfo:procedure.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImProcedure|0.0.1)
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImProcedure|0.0.2)
 </t>
   </si>
   <si>
@@ -1416,7 +1416,7 @@
     <t>DiagnosticReport.composition</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImComposition|0.0.1)
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/imaging-r5/StructureDefinition/ImComposition|0.0.2)
 </t>
   </si>
   <si>
